--- a/output/2025/HaV/table1.xlsx
+++ b/output/2025/HaV/table1.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D236"/>
+  <dimension ref="A1:D234"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -824,7 +824,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ple.27.21-23</t>
+          <t>ple.27.21-32</t>
         </is>
       </c>
       <c r="C24">
@@ -1504,11 +1504,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ple.27.420</t>
+          <t>ple.27.21-32</t>
         </is>
       </c>
       <c r="C58">
-        <v>498.1</v>
+        <v>14461.5</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -1524,11 +1524,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ple.27.21-23</t>
+          <t>ple.27.420</t>
         </is>
       </c>
       <c r="C59">
-        <v>13054.6</v>
+        <v>498.1</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -1804,15 +1804,15 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ple.27.24-32</t>
+          <t>dab.27.22-32</t>
         </is>
       </c>
       <c r="C73">
-        <v>1406.9</v>
+        <v>1599.200000000001</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Rödspätta</t>
+          <t>Sandskädda</t>
         </is>
       </c>
     </row>
@@ -1824,15 +1824,15 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>dab.27.22-32</t>
+          <t>her.27.25-2932</t>
         </is>
       </c>
       <c r="C74">
-        <v>1599.200000000001</v>
+        <v>669.3</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Sandskädda</t>
+          <t>Sill / strömming</t>
         </is>
       </c>
     </row>
@@ -1844,11 +1844,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>her.27.25-2932</t>
+          <t>her.27.3031</t>
         </is>
       </c>
       <c r="C75">
-        <v>669.3</v>
+        <v>180</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -1864,15 +1864,15 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>her.27.3031</t>
+          <t>lumpsucker.27.23.3a</t>
         </is>
       </c>
       <c r="C76">
-        <v>180</v>
+        <v>5476.1</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Sill / strömming</t>
+          <t>Sjurygg</t>
         </is>
       </c>
     </row>
@@ -1884,11 +1884,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>lumpsucker.27.23.3a</t>
+          <t>lumpsucker.27.24-32</t>
         </is>
       </c>
       <c r="C77">
-        <v>5476.1</v>
+        <v>9</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -1904,15 +1904,15 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>lumpsucker.27.24-32</t>
+          <t>bzq.27.2425</t>
         </is>
       </c>
       <c r="C78">
-        <v>9</v>
+        <v>8861.800000000003</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Sjurygg</t>
+          <t>Skrubbskädda</t>
         </is>
       </c>
     </row>
@@ -1924,11 +1924,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>bzq.27.2425</t>
+          <t xml:space="preserve">bwp.27.2729-32 	</t>
         </is>
       </c>
       <c r="C79">
-        <v>8861.800000000003</v>
+        <v>10585</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -1944,11 +1944,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">bwp.27.2729-32 	</t>
+          <t>bzq.27.2628</t>
         </is>
       </c>
       <c r="C80">
-        <v>10585</v>
+        <v>5231</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -1964,11 +1964,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>bzq.27.2628</t>
+          <t>fle.27.2223</t>
         </is>
       </c>
       <c r="C81">
-        <v>5231</v>
+        <v>11179.8</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -1984,15 +1984,15 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>fle.27.2223</t>
+          <t>bll.27.22-32</t>
         </is>
       </c>
       <c r="C82">
-        <v>11179.8</v>
+        <v>948.3000000000001</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Skrubbskädda</t>
+          <t>Slätvar</t>
         </is>
       </c>
     </row>
@@ -2004,15 +2004,15 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>bll.27.22-32</t>
+          <t>cod.27.22-24</t>
         </is>
       </c>
       <c r="C83">
-        <v>948.3000000000001</v>
+        <v>3291.500000000002</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Slätvar</t>
+          <t>Torsk</t>
         </is>
       </c>
     </row>
@@ -2024,11 +2024,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>cod.27.22-24</t>
+          <t>cod.27.24-32</t>
         </is>
       </c>
       <c r="C84">
-        <v>3291.500000000002</v>
+        <v>11267.30000000001</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -2044,15 +2044,15 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>cod.27.24-32</t>
+          <t>ele.2737.nea</t>
         </is>
       </c>
       <c r="C85">
-        <v>11267.30000000001</v>
+        <v>312</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Torsk</t>
+          <t>Ål</t>
         </is>
       </c>
     </row>
@@ -2064,35 +2064,35 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ele.2737.nea</t>
+          <t>trs.27.22-32</t>
         </is>
       </c>
       <c r="C86">
-        <v>312</v>
+        <v>3439.5</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Ål</t>
+          <t>Öring</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Demersalt fiske_Passivt_Östersjön</t>
+          <t>Hummerfiske_Passivt_Västerhavet</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>trs.27.22-32</t>
+          <t>lobster.27.3a</t>
         </is>
       </c>
       <c r="C87">
-        <v>3439.5</v>
+        <v>64505.1</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Öring</t>
+          <t>Hummer</t>
         </is>
       </c>
     </row>
@@ -2104,15 +2104,15 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>lobster.27.3a</t>
+          <t>bcrab.27.3a</t>
         </is>
       </c>
       <c r="C88">
-        <v>64505.1</v>
+        <v>50538.2</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Hummer</t>
+          <t>Krabbtaska</t>
         </is>
       </c>
     </row>
@@ -2124,35 +2124,35 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>bcrab.27.3a</t>
+          <t>cod.27.46a7d20</t>
         </is>
       </c>
       <c r="C89">
-        <v>50538.2</v>
+        <v>35</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Krabbtaska</t>
+          <t>Torsk</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Hummerfiske_Passivt_Västerhavet</t>
+          <t>Kräftburar_Passivt_Västerhavet</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>cod.27.46a7d20</t>
+          <t>caa.27.3a46</t>
         </is>
       </c>
       <c r="C90">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Torsk</t>
+          <t>Havskatt</t>
         </is>
       </c>
     </row>
@@ -2164,15 +2164,15 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>caa.27.3a46</t>
+          <t>nep.fu.3-4</t>
         </is>
       </c>
       <c r="C91">
-        <v>41</v>
+        <v>310338.6000000002</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Havskatt</t>
+          <t>Havskräfta</t>
         </is>
       </c>
     </row>
@@ -2184,15 +2184,15 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>nep.fu.3-4</t>
+          <t>lobster.27.3a</t>
         </is>
       </c>
       <c r="C92">
-        <v>310338.6000000002</v>
+        <v>46.1</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Havskräfta</t>
+          <t>Hummer</t>
         </is>
       </c>
     </row>
@@ -2204,15 +2204,15 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>lobster.27.3a</t>
+          <t>bcrab.27.3a</t>
         </is>
       </c>
       <c r="C93">
-        <v>46.1</v>
+        <v>5706</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Hummer</t>
+          <t>Krabbtaska</t>
         </is>
       </c>
     </row>
@@ -2224,15 +2224,15 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>bcrab.27.3a</t>
+          <t>lin.27.346-91214</t>
         </is>
       </c>
       <c r="C94">
-        <v>5706</v>
+        <v>129</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Krabbtaska</t>
+          <t>Långa</t>
         </is>
       </c>
     </row>
@@ -2244,15 +2244,15 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>lin.27.346-91214</t>
+          <t>pra.27.3a4a</t>
         </is>
       </c>
       <c r="C95">
-        <v>129</v>
+        <v>3</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Långa</t>
+          <t>Nordhavsräka</t>
         </is>
       </c>
     </row>
@@ -2264,15 +2264,15 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>pra.27.3a4a</t>
+          <t>dgs.27.nea</t>
         </is>
       </c>
       <c r="C96">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Nordhavsräka</t>
+          <t>Pigghaj</t>
         </is>
       </c>
     </row>
@@ -2284,15 +2284,15 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>dgs.27.nea</t>
+          <t>wit.27.3a47d</t>
         </is>
       </c>
       <c r="C97">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Pigghaj</t>
+          <t>Rödtunga</t>
         </is>
       </c>
     </row>
@@ -2304,15 +2304,15 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>wit.27.3a47d</t>
+          <t>dab.27.3a4</t>
         </is>
       </c>
       <c r="C98">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Rödtunga</t>
+          <t>Sandskädda</t>
         </is>
       </c>
     </row>
@@ -2324,15 +2324,15 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>dab.27.3a4</t>
+          <t>cod.27.46a7d20</t>
         </is>
       </c>
       <c r="C99">
-        <v>3</v>
+        <v>264.5</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Sandskädda</t>
+          <t>Torsk</t>
         </is>
       </c>
     </row>
@@ -2344,11 +2344,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>cod.27.46a7d20</t>
+          <t>cod.27.21</t>
         </is>
       </c>
       <c r="C100">
-        <v>264.5</v>
+        <v>65</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -2364,35 +2364,35 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>cod.27.21</t>
+          <t>whg.27.3a</t>
         </is>
       </c>
       <c r="C101">
-        <v>65</v>
+        <v>75.5</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Torsk</t>
+          <t>Vitling</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Kräftburar_Passivt_Västerhavet</t>
+          <t>Kräftfiske med rist_Aktivt_Västerhavet</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>whg.27.3a</t>
+          <t>lem.27.3a47d</t>
         </is>
       </c>
       <c r="C102">
-        <v>75.5</v>
+        <v>205.7999999999999</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Vitling</t>
+          <t>Bergtunga</t>
         </is>
       </c>
     </row>
@@ -2404,15 +2404,15 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>lem.27.3a47d</t>
+          <t>pol.27.3a4</t>
         </is>
       </c>
       <c r="C103">
-        <v>205.7999999999999</v>
+        <v>27.5</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Bergtunga</t>
+          <t>Bleka / lyrtorsk</t>
         </is>
       </c>
     </row>
@@ -2424,15 +2424,15 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>pol.27.3a4</t>
+          <t>greatrweaver.27.3a4</t>
         </is>
       </c>
       <c r="C104">
-        <v>27.5</v>
+        <v>21.2</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Bleka / lyrtorsk</t>
+          <t>Fjärsing</t>
         </is>
       </c>
     </row>
@@ -2444,15 +2444,15 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>greatrweaver.27.3a4</t>
+          <t>pok.27.3a46</t>
         </is>
       </c>
       <c r="C105">
-        <v>21.2</v>
+        <v>54.40000000000001</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Fjärsing</t>
+          <t>Gråsej</t>
         </is>
       </c>
     </row>
@@ -2464,15 +2464,15 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>pok.27.3a46</t>
+          <t>caa.27.3a46</t>
         </is>
       </c>
       <c r="C106">
-        <v>54.40000000000001</v>
+        <v>389.9999999999999</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Gråsej</t>
+          <t>Havskatt</t>
         </is>
       </c>
     </row>
@@ -2484,15 +2484,15 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>caa.27.3a46</t>
+          <t>nep.fu.3-4</t>
         </is>
       </c>
       <c r="C107">
-        <v>389.9999999999999</v>
+        <v>817446.9000000028</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Havskatt</t>
+          <t>Havskräfta</t>
         </is>
       </c>
     </row>
@@ -2504,15 +2504,15 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>nep.fu.3-4</t>
+          <t>halibut.27</t>
         </is>
       </c>
       <c r="C108">
-        <v>817446.9000000028</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Havskräfta</t>
+          <t>Hälleflundra</t>
         </is>
       </c>
     </row>
@@ -2524,15 +2524,15 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>halibut.27</t>
+          <t>rjc.27.3a47d</t>
         </is>
       </c>
       <c r="C109">
-        <v>9.300000000000001</v>
+        <v>175</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Hälleflundra</t>
+          <t>Knaggrocka</t>
         </is>
       </c>
     </row>
@@ -2544,15 +2544,15 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>rjc.27.3a47d</t>
+          <t>gug.27.3a47d</t>
         </is>
       </c>
       <c r="C110">
-        <v>175</v>
+        <v>198.6</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Knaggrocka</t>
+          <t>Knot</t>
         </is>
       </c>
     </row>
@@ -2564,15 +2564,15 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>gug.27.3a47d</t>
+          <t>had.27.46a20</t>
         </is>
       </c>
       <c r="C111">
-        <v>198.6</v>
+        <v>271.1999999999999</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Knot</t>
+          <t>Kolja</t>
         </is>
       </c>
     </row>
@@ -2584,15 +2584,15 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>had.27.46a20</t>
+          <t>bcrab.27.3a</t>
         </is>
       </c>
       <c r="C112">
-        <v>271.1999999999999</v>
+        <v>43.1</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Kolja</t>
+          <t>Krabbtaska</t>
         </is>
       </c>
     </row>
@@ -2604,15 +2604,15 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>bcrab.27.3a</t>
+          <t>hke.27.3a46-8abd</t>
         </is>
       </c>
       <c r="C113">
-        <v>43.1</v>
+        <v>210.3</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Krabbtaska</t>
+          <t>Kummel</t>
         </is>
       </c>
     </row>
@@ -2624,15 +2624,15 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>hke.27.3a46-8abd</t>
+          <t>lin.27.346-91214</t>
         </is>
       </c>
       <c r="C114">
-        <v>210.3</v>
+        <v>65.99999999999999</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Kummel</t>
+          <t>Långa</t>
         </is>
       </c>
     </row>
@@ -2644,15 +2644,15 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>lin.27.346-91214</t>
+          <t>mac.27.nea</t>
         </is>
       </c>
       <c r="C115">
-        <v>65.99999999999999</v>
+        <v>390.3</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Långa</t>
+          <t>Makrill</t>
         </is>
       </c>
     </row>
@@ -2664,15 +2664,15 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>mac.27.nea</t>
+          <t>anf.27.3a46</t>
         </is>
       </c>
       <c r="C116">
-        <v>390.3</v>
+        <v>619.5999999999996</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Makrill</t>
+          <t>Marulk</t>
         </is>
       </c>
     </row>
@@ -2684,15 +2684,15 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>anf.27.3a46</t>
+          <t>pra.27.3a4a</t>
         </is>
       </c>
       <c r="C117">
-        <v>619.5999999999996</v>
+        <v>665.0000000000005</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Marulk</t>
+          <t>Nordhavsräka</t>
         </is>
       </c>
     </row>
@@ -2704,15 +2704,15 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>pra.27.3a4a</t>
+          <t>dgs.27.nea</t>
         </is>
       </c>
       <c r="C118">
-        <v>665.0000000000005</v>
+        <v>1815.6</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Nordhavsräka</t>
+          <t>Pigghaj</t>
         </is>
       </c>
     </row>
@@ -2724,15 +2724,15 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>dgs.27.nea</t>
+          <t>tur.27.3a</t>
         </is>
       </c>
       <c r="C119">
-        <v>1815.6</v>
+        <v>483.8000000000001</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Pigghaj</t>
+          <t>Piggvar</t>
         </is>
       </c>
     </row>
@@ -2744,15 +2744,15 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>tur.27.3a</t>
+          <t>ple.27.420</t>
         </is>
       </c>
       <c r="C120">
-        <v>483.8000000000001</v>
+        <v>1081.600000000001</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Piggvar</t>
+          <t>Rödspätta</t>
         </is>
       </c>
     </row>
@@ -2764,11 +2764,11 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ple.27.420</t>
+          <t>ple.27.21-32</t>
         </is>
       </c>
       <c r="C121">
-        <v>1081.600000000001</v>
+        <v>669</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -2784,15 +2784,15 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ple.27.21-23</t>
+          <t>wit.27.3a47d</t>
         </is>
       </c>
       <c r="C122">
-        <v>669</v>
+        <v>219.0999999999998</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Rödspätta</t>
+          <t>Rödtunga</t>
         </is>
       </c>
     </row>
@@ -2804,15 +2804,15 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>wit.27.3a47d</t>
+          <t>dab.27.3a4</t>
         </is>
       </c>
       <c r="C123">
-        <v>219.0999999999998</v>
+        <v>667.5</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Rödtunga</t>
+          <t>Sandskädda</t>
         </is>
       </c>
     </row>
@@ -2824,15 +2824,15 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>dab.27.3a4</t>
+          <t>her.27.3a47d</t>
         </is>
       </c>
       <c r="C124">
-        <v>667.5</v>
+        <v>148.4</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Sandskädda</t>
+          <t>Sill / strömming</t>
         </is>
       </c>
     </row>
@@ -2844,15 +2844,15 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>her.27.3a47d</t>
+          <t>fle.27.3a4</t>
         </is>
       </c>
       <c r="C125">
-        <v>148.4</v>
+        <v>129.6</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Sill / strömming</t>
+          <t>Skrubbskädda</t>
         </is>
       </c>
     </row>
@@ -2864,15 +2864,15 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>fle.27.3a4</t>
+          <t>bll.27.3a47de</t>
         </is>
       </c>
       <c r="C126">
-        <v>129.6</v>
+        <v>2584.799999999998</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Skrubbskädda</t>
+          <t>Slätvar</t>
         </is>
       </c>
     </row>
@@ -2884,15 +2884,15 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>bll.27.3a47de</t>
+          <t>hom.27.3a4bc7d</t>
         </is>
       </c>
       <c r="C127">
-        <v>2584.799999999998</v>
+        <v>2</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Slätvar</t>
+          <t>Taggmakrill</t>
         </is>
       </c>
     </row>
@@ -2904,15 +2904,15 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>hom.27.3a4bc7d</t>
+          <t>cod.27.46a7d20</t>
         </is>
       </c>
       <c r="C128">
-        <v>2</v>
+        <v>684.2000000000002</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Taggmakrill</t>
+          <t>Torsk</t>
         </is>
       </c>
     </row>
@@ -2924,11 +2924,11 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>cod.27.46a7d20</t>
+          <t>cod.27.21</t>
         </is>
       </c>
       <c r="C129">
-        <v>684.2000000000002</v>
+        <v>481.4999999999999</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -2944,15 +2944,15 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>cod.27.21</t>
+          <t>whg.27.3a</t>
         </is>
       </c>
       <c r="C130">
-        <v>481.4999999999999</v>
+        <v>1455.500000000002</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Torsk</t>
+          <t>Vitling</t>
         </is>
       </c>
     </row>
@@ -2964,35 +2964,35 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>whg.27.3a</t>
+          <t>sol.27.20-24</t>
         </is>
       </c>
       <c r="C131">
-        <v>1455.500000000002</v>
+        <v>804.1000000000009</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Vitling</t>
+          <t>Äkta tunga</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Kräftfiske med rist_Aktivt_Västerhavet</t>
+          <t>Laxfiske_Passivt_Östersjön</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>sol.27.20-24</t>
+          <t>sal.27.22-31</t>
         </is>
       </c>
       <c r="C132">
-        <v>804.1000000000009</v>
+        <v>103618</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Äkta tunga</t>
+          <t>Lax</t>
         </is>
       </c>
     </row>
@@ -3004,15 +3004,15 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>sal.27.22-31</t>
+          <t>ven.27.3031</t>
         </is>
       </c>
       <c r="C133">
-        <v>103618</v>
+        <v>170</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Lax</t>
+          <t>Siklöja</t>
         </is>
       </c>
     </row>
@@ -3024,15 +3024,15 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ven.27.3031</t>
+          <t>her.27.3031</t>
         </is>
       </c>
       <c r="C134">
-        <v>170</v>
+        <v>43</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Siklöja</t>
+          <t>Sill / strömming</t>
         </is>
       </c>
     </row>
@@ -3044,15 +3044,15 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>her.27.3031</t>
+          <t>cod.27.22-24</t>
         </is>
       </c>
       <c r="C135">
-        <v>43</v>
+        <v>99.5</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Sill / strömming</t>
+          <t>Torsk</t>
         </is>
       </c>
     </row>
@@ -3064,35 +3064,35 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>cod.27.22-24</t>
+          <t>trs.27.22-32</t>
         </is>
       </c>
       <c r="C136">
-        <v>99.5</v>
+        <v>4627.399999999999</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Torsk</t>
+          <t>Öring</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Laxfiske_Passivt_Östersjön</t>
+          <t>Pelagiskt fiske_Aktivt_Västerhavet</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>trs.27.22-32</t>
+          <t>whb.27.1-91214</t>
         </is>
       </c>
       <c r="C137">
-        <v>4627.399999999999</v>
+        <v>767387</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Öring</t>
+          <t>Blåvitling</t>
         </is>
       </c>
     </row>
@@ -3104,15 +3104,15 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>whb.27.1-91214</t>
+          <t>greatrweaver.27.3a4</t>
         </is>
       </c>
       <c r="C138">
-        <v>767387</v>
+        <v>200</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Blåvitling</t>
+          <t>Fjärsing</t>
         </is>
       </c>
     </row>
@@ -3124,15 +3124,15 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>greatrweaver.27.3a4</t>
+          <t>pok.27.3a46</t>
         </is>
       </c>
       <c r="C139">
-        <v>200</v>
+        <v>6860</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Fjärsing</t>
+          <t>Gråsej</t>
         </is>
       </c>
     </row>
@@ -3144,15 +3144,15 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>pok.27.3a46</t>
+          <t>gug.27.3a47d</t>
         </is>
       </c>
       <c r="C140">
-        <v>6860</v>
+        <v>13100</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Gråsej</t>
+          <t>Knot</t>
         </is>
       </c>
     </row>
@@ -3164,15 +3164,15 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>gug.27.3a47d</t>
+          <t>had.27.46a20</t>
         </is>
       </c>
       <c r="C141">
-        <v>13100</v>
+        <v>68247</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Knot</t>
+          <t>Kolja</t>
         </is>
       </c>
     </row>
@@ -3184,15 +3184,15 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>had.27.46a20</t>
+          <t>hke.27.3a46-8abd</t>
         </is>
       </c>
       <c r="C142">
-        <v>68247</v>
+        <v>30</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Kolja</t>
+          <t>Kummel</t>
         </is>
       </c>
     </row>
@@ -3204,15 +3204,15 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>hke.27.3a46-8abd</t>
+          <t>mac.27.nea</t>
         </is>
       </c>
       <c r="C143">
-        <v>30</v>
+        <v>1797062</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Kummel</t>
+          <t>Makrill</t>
         </is>
       </c>
     </row>
@@ -3224,15 +3224,15 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>mac.27.nea</t>
+          <t>dgs.27.nea</t>
         </is>
       </c>
       <c r="C144">
-        <v>1797062</v>
+        <v>65</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Makrill</t>
+          <t>Pigghaj</t>
         </is>
       </c>
     </row>
@@ -3244,15 +3244,15 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>dgs.27.nea</t>
+          <t>ple.27.21-32</t>
         </is>
       </c>
       <c r="C145">
-        <v>65</v>
+        <v>18.1</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Pigghaj</t>
+          <t>Rödspätta</t>
         </is>
       </c>
     </row>
@@ -3564,15 +3564,15 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ple.27.24-32</t>
+          <t>ven.27.3031</t>
         </is>
       </c>
       <c r="C161">
-        <v>18.1</v>
+        <v>6410</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Rödspätta</t>
+          <t>Siklöja</t>
         </is>
       </c>
     </row>
@@ -3584,15 +3584,15 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ven.27.3031</t>
+          <t>her.27.20-24</t>
         </is>
       </c>
       <c r="C162">
-        <v>6410</v>
+        <v>234082.0000000001</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Siklöja</t>
+          <t>Sill / strömming</t>
         </is>
       </c>
     </row>
@@ -3604,11 +3604,11 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>her.27.20-24</t>
+          <t>her.27.25-2932</t>
         </is>
       </c>
       <c r="C163">
-        <v>234082.0000000001</v>
+        <v>9132326.000000002</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -3624,11 +3624,11 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>her.27.25-2932</t>
+          <t>her.27.3031</t>
         </is>
       </c>
       <c r="C164">
-        <v>9132326.000000002</v>
+        <v>9100270.500000002</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -3644,15 +3644,15 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>her.27.3031</t>
+          <t>lumpsucker.27.24-32</t>
         </is>
       </c>
       <c r="C165">
-        <v>9100270.500000002</v>
+        <v>187.4</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Sill / strömming</t>
+          <t>Sjurygg</t>
         </is>
       </c>
     </row>
@@ -3664,15 +3664,15 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>lumpsucker.27.24-32</t>
+          <t>spr.27.22-32</t>
         </is>
       </c>
       <c r="C166">
-        <v>187.4</v>
+        <v>39161770.50000001</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Sjurygg</t>
+          <t>Skarpsill</t>
         </is>
       </c>
     </row>
@@ -3684,15 +3684,15 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>spr.27.22-32</t>
+          <t>bzq.27.2425</t>
         </is>
       </c>
       <c r="C167">
-        <v>39161770.50000001</v>
+        <v>3516.5</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Skarpsill</t>
+          <t>Skrubbskädda</t>
         </is>
       </c>
     </row>
@@ -3704,11 +3704,11 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>bzq.27.2425</t>
+          <t>bzq.27.2628</t>
         </is>
       </c>
       <c r="C168">
-        <v>3516.5</v>
+        <v>2712</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -3724,15 +3724,15 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>bzq.27.2628</t>
+          <t>cod.27.24-32</t>
         </is>
       </c>
       <c r="C169">
-        <v>2712</v>
+        <v>3852.399999999989</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Skrubbskädda</t>
+          <t>Torsk</t>
         </is>
       </c>
     </row>
@@ -3744,11 +3744,11 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>cod.27.24-32</t>
+          <t>cod.27.22-24</t>
         </is>
       </c>
       <c r="C170">
-        <v>3852.399999999989</v>
+        <v>212</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -3759,20 +3759,20 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Pelagiskt fiske_Aktivt_Östersjön</t>
+          <t>Pelagiskt fiske_Passivt_Västerhavet</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>cod.27.22-24</t>
+          <t>greatrweaver.27.3a4</t>
         </is>
       </c>
       <c r="C171">
-        <v>212</v>
+        <v>48</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Torsk</t>
+          <t>Fjärsing</t>
         </is>
       </c>
     </row>
@@ -3784,15 +3784,15 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>greatrweaver.27.3a4</t>
+          <t>pok.27.3a46</t>
         </is>
       </c>
       <c r="C172">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Fjärsing</t>
+          <t>Gråsej</t>
         </is>
       </c>
     </row>
@@ -3804,15 +3804,15 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>pok.27.3a46</t>
+          <t>gug.27.3a47d</t>
         </is>
       </c>
       <c r="C173">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Gråsej</t>
+          <t>Knot</t>
         </is>
       </c>
     </row>
@@ -3824,15 +3824,15 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>gug.27.3a47d</t>
+          <t>mac.27.nea</t>
         </is>
       </c>
       <c r="C174">
-        <v>2</v>
+        <v>187279</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Knot</t>
+          <t>Makrill</t>
         </is>
       </c>
     </row>
@@ -3844,15 +3844,15 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>mac.27.nea</t>
+          <t>dgs.27.nea</t>
         </is>
       </c>
       <c r="C175">
-        <v>187279</v>
+        <v>1970</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Makrill</t>
+          <t>Pigghaj</t>
         </is>
       </c>
     </row>
@@ -3864,15 +3864,15 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>dgs.27.nea</t>
+          <t>ple.27.21-32</t>
         </is>
       </c>
       <c r="C176">
-        <v>1970</v>
+        <v>21</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Pigghaj</t>
+          <t>Rödspätta</t>
         </is>
       </c>
     </row>
@@ -3884,15 +3884,15 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>ple.27.21-23</t>
+          <t>her.27.3a47d</t>
         </is>
       </c>
       <c r="C177">
-        <v>4</v>
+        <v>134376</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Rödspätta</t>
+          <t>Sill / strömming</t>
         </is>
       </c>
     </row>
@@ -3904,15 +3904,15 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>her.27.3a47d</t>
+          <t>spr.27.3a4</t>
         </is>
       </c>
       <c r="C178">
-        <v>134376</v>
+        <v>5</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Sill / strömming</t>
+          <t>Skarpsill</t>
         </is>
       </c>
     </row>
@@ -3924,15 +3924,15 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>spr.27.3a4</t>
+          <t>cod.27.46a7d20</t>
         </is>
       </c>
       <c r="C179">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Skarpsill</t>
+          <t>Torsk</t>
         </is>
       </c>
     </row>
@@ -3944,15 +3944,15 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>cod.27.46a7d20</t>
+          <t>whg.27.3a</t>
         </is>
       </c>
       <c r="C180">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Torsk</t>
+          <t>Vitling</t>
         </is>
       </c>
     </row>
@@ -3964,35 +3964,35 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>whg.27.3a</t>
+          <t>sol.27.20-24</t>
         </is>
       </c>
       <c r="C181">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Vitling</t>
+          <t>Äkta tunga</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Pelagiskt fiske_Passivt_Västerhavet</t>
+          <t>Pelagiskt fiske_Passivt_Östersjön</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>sol.27.20-24</t>
+          <t>mac.27.nea</t>
         </is>
       </c>
       <c r="C182">
-        <v>3</v>
+        <v>6575</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Äkta tunga</t>
+          <t>Makrill</t>
         </is>
       </c>
     </row>
@@ -4004,15 +4004,15 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>mac.27.nea</t>
+          <t>ven.27.3031</t>
         </is>
       </c>
       <c r="C183">
-        <v>6575</v>
+        <v>14290</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Makrill</t>
+          <t>Siklöja</t>
         </is>
       </c>
     </row>
@@ -4024,15 +4024,15 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>ple.27.24-32</t>
+          <t>her.27.20-24</t>
         </is>
       </c>
       <c r="C184">
-        <v>17</v>
+        <v>114487</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Rödspätta</t>
+          <t>Sill / strömming</t>
         </is>
       </c>
     </row>
@@ -4044,15 +4044,15 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>ven.27.3031</t>
+          <t>her.27.25-2932</t>
         </is>
       </c>
       <c r="C185">
-        <v>14290</v>
+        <v>122865.2</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Siklöja</t>
+          <t>Sill / strömming</t>
         </is>
       </c>
     </row>
@@ -4064,11 +4064,11 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>her.27.20-24</t>
+          <t>her.27.3031</t>
         </is>
       </c>
       <c r="C186">
-        <v>114487</v>
+        <v>329376</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -4084,15 +4084,15 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>her.27.25-2932</t>
+          <t>fle.27.2223</t>
         </is>
       </c>
       <c r="C187">
-        <v>122865.2</v>
+        <v>8</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Sill / strömming</t>
+          <t>Skrubbskädda</t>
         </is>
       </c>
     </row>
@@ -4104,15 +4104,15 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>her.27.3031</t>
+          <t>cod.27.24-32</t>
         </is>
       </c>
       <c r="C188">
-        <v>329376</v>
+        <v>11.6</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Sill / strömming</t>
+          <t>Torsk</t>
         </is>
       </c>
     </row>
@@ -4124,55 +4124,55 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>fle.27.2223</t>
+          <t>trs.27.22-32</t>
         </is>
       </c>
       <c r="C189">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Skrubbskädda</t>
+          <t>Öring</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Pelagiskt fiske_Passivt_Östersjön</t>
+          <t>Räkfiske_Aktivt_Västerhavet</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>cod.27.24-32</t>
+          <t>lem.27.3a47d</t>
         </is>
       </c>
       <c r="C190">
-        <v>11.6</v>
+        <v>16.7</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Torsk</t>
+          <t>Bergtunga</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Pelagiskt fiske_Passivt_Östersjön</t>
+          <t>Räkfiske_Aktivt_Västerhavet</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>trs.27.22-32</t>
+          <t>pol.27.3a4</t>
         </is>
       </c>
       <c r="C191">
-        <v>23</v>
+        <v>557.5000000000001</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Öring</t>
+          <t>Bleka / lyrtorsk</t>
         </is>
       </c>
     </row>
@@ -4184,15 +4184,15 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>lem.27.3a47d</t>
+          <t>whb.27.1-91214</t>
         </is>
       </c>
       <c r="C192">
-        <v>16.7</v>
+        <v>190</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Bergtunga</t>
+          <t>Blåvitling</t>
         </is>
       </c>
     </row>
@@ -4204,15 +4204,15 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>pol.27.3a4</t>
+          <t>pok.27.3a46</t>
         </is>
       </c>
       <c r="C193">
-        <v>557.5000000000001</v>
+        <v>45728.70000000014</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Bleka / lyrtorsk</t>
+          <t>Gråsej</t>
         </is>
       </c>
     </row>
@@ -4224,15 +4224,15 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>whb.27.1-91214</t>
+          <t>caa.27.3a46</t>
         </is>
       </c>
       <c r="C194">
-        <v>190</v>
+        <v>12</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Blåvitling</t>
+          <t>Havskatt</t>
         </is>
       </c>
     </row>
@@ -4244,15 +4244,15 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>pok.27.3a46</t>
+          <t>nep.fu.3-4</t>
         </is>
       </c>
       <c r="C195">
-        <v>45728.70000000014</v>
+        <v>4202.700000000003</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Gråsej</t>
+          <t>Havskräfta</t>
         </is>
       </c>
     </row>
@@ -4264,15 +4264,15 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>caa.27.3a46</t>
+          <t>halibut.27</t>
         </is>
       </c>
       <c r="C196">
-        <v>12</v>
+        <v>901.3000000000002</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Havskatt</t>
+          <t>Hälleflundra</t>
         </is>
       </c>
     </row>
@@ -4284,15 +4284,15 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>nep.fu.3-4</t>
+          <t>rjc.27.3a47d</t>
         </is>
       </c>
       <c r="C197">
-        <v>4202.700000000003</v>
+        <v>53</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Havskräfta</t>
+          <t>Knaggrocka</t>
         </is>
       </c>
     </row>
@@ -4304,15 +4304,15 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>halibut.27</t>
+          <t>gug.27.3a47d</t>
         </is>
       </c>
       <c r="C198">
-        <v>901.3000000000002</v>
+        <v>1</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Hälleflundra</t>
+          <t>Knot</t>
         </is>
       </c>
     </row>
@@ -4324,15 +4324,15 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>rjc.27.3a47d</t>
+          <t>had.27.46a20</t>
         </is>
       </c>
       <c r="C199">
-        <v>53</v>
+        <v>8375.900000000018</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Knaggrocka</t>
+          <t>Kolja</t>
         </is>
       </c>
     </row>
@@ -4344,15 +4344,15 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>gug.27.3a47d</t>
+          <t>hke.27.3a46-8abd</t>
         </is>
       </c>
       <c r="C200">
-        <v>1</v>
+        <v>2650.900000000001</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Knot</t>
+          <t>Kummel</t>
         </is>
       </c>
     </row>
@@ -4364,15 +4364,15 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>had.27.46a20</t>
+          <t>lin.27.346-91214</t>
         </is>
       </c>
       <c r="C201">
-        <v>8375.900000000018</v>
+        <v>8653.199999999995</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Kolja</t>
+          <t>Långa</t>
         </is>
       </c>
     </row>
@@ -4384,15 +4384,15 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>hke.27.3a46-8abd</t>
+          <t>mac.27.nea</t>
         </is>
       </c>
       <c r="C202">
-        <v>2650.900000000001</v>
+        <v>1</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Kummel</t>
+          <t>Makrill</t>
         </is>
       </c>
     </row>
@@ -4404,15 +4404,15 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>lin.27.346-91214</t>
+          <t>anf.27.3a46</t>
         </is>
       </c>
       <c r="C203">
-        <v>8653.199999999995</v>
+        <v>14681.60000000001</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Långa</t>
+          <t>Marulk</t>
         </is>
       </c>
     </row>
@@ -4424,15 +4424,15 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>mac.27.nea</t>
+          <t>pra.27.3a4a</t>
         </is>
       </c>
       <c r="C204">
-        <v>1</v>
+        <v>820810.6000000016</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Makrill</t>
+          <t>Nordhavsräka</t>
         </is>
       </c>
     </row>
@@ -4444,15 +4444,15 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>anf.27.3a46</t>
+          <t>dgs.27.nea</t>
         </is>
       </c>
       <c r="C205">
-        <v>14681.60000000001</v>
+        <v>32</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Marulk</t>
+          <t>Pigghaj</t>
         </is>
       </c>
     </row>
@@ -4464,15 +4464,15 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>pra.27.3a4a</t>
+          <t>tur.27.3a</t>
         </is>
       </c>
       <c r="C206">
-        <v>820810.6000000016</v>
+        <v>32.4</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Nordhavsräka</t>
+          <t>Piggvar</t>
         </is>
       </c>
     </row>
@@ -4484,15 +4484,15 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>dgs.27.nea</t>
+          <t>tur.27.4</t>
         </is>
       </c>
       <c r="C207">
-        <v>32</v>
+        <v>3.9</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Pigghaj</t>
+          <t>Piggvar</t>
         </is>
       </c>
     </row>
@@ -4504,15 +4504,15 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>tur.27.3a</t>
+          <t>ple.27.420</t>
         </is>
       </c>
       <c r="C208">
-        <v>32.4</v>
+        <v>687.3000000000006</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Piggvar</t>
+          <t>Rödspätta</t>
         </is>
       </c>
     </row>
@@ -4524,15 +4524,15 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>tur.27.4</t>
+          <t>ple.27.21-32</t>
         </is>
       </c>
       <c r="C209">
-        <v>3.9</v>
+        <v>7.4</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Piggvar</t>
+          <t>Rödspätta</t>
         </is>
       </c>
     </row>
@@ -4544,15 +4544,15 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>ple.27.420</t>
+          <t>wit.27.3a47d</t>
         </is>
       </c>
       <c r="C210">
-        <v>687.3000000000006</v>
+        <v>3937.599999999992</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Rödspätta</t>
+          <t>Rödtunga</t>
         </is>
       </c>
     </row>
@@ -4564,15 +4564,15 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>ple.27.21-23</t>
+          <t>her.27.3a47d</t>
         </is>
       </c>
       <c r="C211">
-        <v>7.4</v>
+        <v>177.6</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Rödspätta</t>
+          <t>Sill / strömming</t>
         </is>
       </c>
     </row>
@@ -4584,15 +4584,15 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>wit.27.3a47d</t>
+          <t>lumpsucker.27.23.3a</t>
         </is>
       </c>
       <c r="C212">
-        <v>3937.599999999992</v>
+        <v>15.3</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Rödtunga</t>
+          <t>Sjurygg</t>
         </is>
       </c>
     </row>
@@ -4604,15 +4604,15 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>her.27.3a47d</t>
+          <t>rng.27.3a</t>
         </is>
       </c>
       <c r="C213">
-        <v>177.6</v>
+        <v>26</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Sill / strömming</t>
+          <t>Skoläst</t>
         </is>
       </c>
     </row>
@@ -4624,15 +4624,15 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>lumpsucker.27.23.3a</t>
+          <t>bll.27.3a47de</t>
         </is>
       </c>
       <c r="C214">
-        <v>15.3</v>
+        <v>19.3</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Sjurygg</t>
+          <t>Slätvar</t>
         </is>
       </c>
     </row>
@@ -4644,15 +4644,15 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>rng.27.3a</t>
+          <t>cod.27.46a7d20</t>
         </is>
       </c>
       <c r="C215">
-        <v>26</v>
+        <v>37523.59999999999</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Skoläst</t>
+          <t>Torsk</t>
         </is>
       </c>
     </row>
@@ -4664,15 +4664,15 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>bll.27.3a47de</t>
+          <t>cod.27.21</t>
         </is>
       </c>
       <c r="C216">
-        <v>19.3</v>
+        <v>0.5</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Slätvar</t>
+          <t>Torsk</t>
         </is>
       </c>
     </row>
@@ -4684,15 +4684,15 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>cod.27.46a7d20</t>
+          <t>whg.27.47d</t>
         </is>
       </c>
       <c r="C217">
-        <v>37523.59999999999</v>
+        <v>120.4</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Torsk</t>
+          <t>Vitling</t>
         </is>
       </c>
     </row>
@@ -4704,15 +4704,15 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>cod.27.21</t>
+          <t>whg.27.3a</t>
         </is>
       </c>
       <c r="C218">
-        <v>0.5</v>
+        <v>232.1000000000001</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Torsk</t>
+          <t>Vitling</t>
         </is>
       </c>
     </row>
@@ -4724,15 +4724,15 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>whg.27.47d</t>
+          <t>nop.27.3a4</t>
         </is>
       </c>
       <c r="C219">
-        <v>120.4</v>
+        <v>26198.90000000001</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Vitling</t>
+          <t>Vitlinglyra</t>
         </is>
       </c>
     </row>
@@ -4744,115 +4744,115 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>whg.27.3a</t>
+          <t>sol.27.20-24</t>
         </is>
       </c>
       <c r="C220">
-        <v>232.1000000000001</v>
+        <v>3</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Vitling</t>
+          <t>Äkta tunga</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Räkfiske_Aktivt_Västerhavet</t>
+          <t>Siklöjefiske_Aktivt_Östersjön</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>nop.27.3a4</t>
+          <t>ven.27.3031</t>
         </is>
       </c>
       <c r="C221">
-        <v>26198.90000000001</v>
+        <v>1604224</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Vitlinglyra</t>
+          <t>Siklöja</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Räkfiske_Aktivt_Västerhavet</t>
+          <t>Siklöjefiske_Aktivt_Östersjön</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>sol.27.20-24</t>
+          <t>her.27.3031</t>
         </is>
       </c>
       <c r="C222">
-        <v>3</v>
+        <v>67661.00000000001</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Äkta tunga</t>
+          <t>Sill / strömming</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Siklöjefiske_Aktivt_Östersjön</t>
+          <t>Ålfiske_Passivt_Västerhavet</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>ven.27.3031</t>
+          <t>sol.27.20-24</t>
         </is>
       </c>
       <c r="C223">
-        <v>1604224</v>
+        <v>24</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Siklöja</t>
+          <t>Äkta tunga</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Siklöjefiske_Aktivt_Östersjön</t>
+          <t>Ålfiske_Passivt_Östersjön</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>her.27.3031</t>
+          <t>tur.27.22-32</t>
         </is>
       </c>
       <c r="C224">
-        <v>67661.00000000001</v>
+        <v>26</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Sill / strömming</t>
+          <t>Piggvar</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Ålfiske_Passivt_Västerhavet</t>
+          <t>Ålfiske_Passivt_Östersjön</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>sol.27.20-24</t>
+          <t>dab.27.22-32</t>
         </is>
       </c>
       <c r="C225">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Äkta tunga</t>
+          <t>Sandskädda</t>
         </is>
       </c>
     </row>
@@ -4864,15 +4864,15 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>tur.27.22-32</t>
+          <t>her.27.20-24</t>
         </is>
       </c>
       <c r="C226">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Piggvar</t>
+          <t>Sill / strömming</t>
         </is>
       </c>
     </row>
@@ -4884,15 +4884,15 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>dab.27.22-32</t>
+          <t>her.27.25-2932</t>
         </is>
       </c>
       <c r="C227">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Sandskädda</t>
+          <t>Sill / strömming</t>
         </is>
       </c>
     </row>
@@ -4904,15 +4904,15 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>her.27.20-24</t>
+          <t>bzq.27.2425</t>
         </is>
       </c>
       <c r="C228">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Sill / strömming</t>
+          <t>Skrubbskädda</t>
         </is>
       </c>
     </row>
@@ -4924,15 +4924,15 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>her.27.25-2932</t>
+          <t xml:space="preserve">bwp.27.2729-32 	</t>
         </is>
       </c>
       <c r="C229">
-        <v>66</v>
+        <v>1172</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Sill / strömming</t>
+          <t>Skrubbskädda</t>
         </is>
       </c>
     </row>
@@ -4944,11 +4944,11 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>bzq.27.2425</t>
+          <t>fle.27.2223</t>
         </is>
       </c>
       <c r="C230">
-        <v>107</v>
+        <v>25</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -4964,15 +4964,15 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t xml:space="preserve">bwp.27.2729-32 	</t>
+          <t>bll.27.22-32</t>
         </is>
       </c>
       <c r="C231">
-        <v>1172</v>
+        <v>1</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Skrubbskädda</t>
+          <t>Slätvar</t>
         </is>
       </c>
     </row>
@@ -4984,15 +4984,15 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>fle.27.2223</t>
+          <t>cod.27.24-32</t>
         </is>
       </c>
       <c r="C232">
-        <v>25</v>
+        <v>154.9999999999999</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Skrubbskädda</t>
+          <t>Torsk</t>
         </is>
       </c>
     </row>
@@ -5004,15 +5004,15 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>bll.27.22-32</t>
+          <t>ele.2737.nea</t>
         </is>
       </c>
       <c r="C233">
-        <v>1</v>
+        <v>102601.5</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Slätvar</t>
+          <t>Ål</t>
         </is>
       </c>
     </row>
@@ -5024,53 +5024,13 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>cod.27.24-32</t>
+          <t>trs.27.22-32</t>
         </is>
       </c>
       <c r="C234">
-        <v>154.9999999999999</v>
+        <v>220.5</v>
       </c>
       <c r="D234" t="inlineStr">
-        <is>
-          <t>Torsk</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>Ålfiske_Passivt_Östersjön</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>ele.2737.nea</t>
-        </is>
-      </c>
-      <c r="C235">
-        <v>102601.5</v>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>Ål</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>Ålfiske_Passivt_Östersjön</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>trs.27.22-32</t>
-        </is>
-      </c>
-      <c r="C236">
-        <v>220.5</v>
-      </c>
-      <c r="D236" t="inlineStr">
         <is>
           <t>Öring</t>
         </is>
